--- a/StructureDefinition-ncpi-research-study.xlsx
+++ b/StructureDefinition-ncpi-research-study.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -372,7 +372,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -503,7 +503,7 @@
 </t>
   </si>
   <si>
-    <t>URL describing the policy restrictions in detail.</t>
+    <t>Statement investigators should include to acknowledge use data from this study. This can include, but is not limited to, funding sources, organizational affiliations, or sponsors.</t>
   </si>
   <si>
     <t>Provides an informative description of acknowledgement expectations for those using data from the research study.</t>
@@ -582,7 +582,7 @@
     <t>ResearchStudy.protocol</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(PlanDefinition)
+    <t xml:space="preserve">Reference(PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -608,7 +608,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ResearchStudy)
+    <t xml:space="preserve">Reference(ResearchStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -673,7 +673,7 @@
     <t>Codes for the main intent of the study.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.primaryPurposeTypeCode</t>
@@ -694,7 +694,7 @@
     <t>Codes for the stage in the progression of a therapy from initial experimental use in humans in clinical trials to post-market evaluation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-phase</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-phase|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.phaseCode</t>
@@ -846,7 +846,7 @@
     <t>Identification of the condition or diagnosis.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>StudyCondition.code</t>
@@ -923,7 +923,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.participatingLocationCode</t>
@@ -955,7 +955,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Group)
+    <t xml:space="preserve">Reference(Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1012,7 +1012,7 @@
     <t>ResearchStudy.sponsor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1037,7 +1037,7 @@
     <t>ResearchStudy.principalInvestigator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1056,7 +1056,7 @@
     <t>ResearchStudy.site</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1087,7 +1087,7 @@
     <t>Codes for why the study ended prematurely.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped|4.0.1</t>
   </si>
   <si>
     <t>StudyOverallStatus.studyStoppedReasonCode</t>
@@ -1250,7 +1250,7 @@
     <t>Codes for the kind of study objective.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type|4.0.1</t>
   </si>
   <si>
     <t>StudyObjective.typeCode</t>
@@ -1583,7 +1583,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="106.90234375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.12890625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.65625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-ncpi-research-study.xlsx
+++ b/StructureDefinition-ncpi-research-study.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-ncpi-research-study.xlsx
+++ b/StructureDefinition-ncpi-research-study.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-research-study.xlsx
+++ b/StructureDefinition-ncpi-research-study.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-research-study.xlsx
+++ b/StructureDefinition-ncpi-research-study.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
